--- a/AAII_Financials/Quarterly/DEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>DEC</t>
   </si>
@@ -656,109 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45473</v>
       </c>
       <c r="K7" s="2">
         <v>45473</v>
       </c>
       <c r="L7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>520900</v>
+      </c>
+      <c r="E8" s="3">
         <v>575500</v>
-      </c>
-      <c r="E8" s="3">
-        <v>436600</v>
       </c>
       <c r="F8" s="3">
         <v>436600</v>
       </c>
       <c r="G8" s="3">
+        <v>436600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>417600</v>
+      </c>
+      <c r="I8" s="3">
         <v>346800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>223100</v>
-      </c>
-      <c r="I8" s="3">
-        <v>223100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>174300</v>
       </c>
       <c r="K8" s="3">
         <v>174300</v>
@@ -767,48 +772,51 @@
         <v>174300</v>
       </c>
       <c r="M8" s="3">
-        <v>175400</v>
+        <v>174300</v>
       </c>
       <c r="N8" s="3">
         <v>175400</v>
       </c>
       <c r="O8" s="3">
-        <v>228000</v>
+        <v>175400</v>
       </c>
       <c r="P8" s="3">
         <v>228000</v>
       </c>
       <c r="Q8" s="3">
-        <v>472900</v>
+        <v>228000</v>
       </c>
       <c r="R8" s="3">
         <v>472900</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>472900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>215700</v>
+      </c>
+      <c r="E9" s="3">
         <v>212300</v>
-      </c>
-      <c r="E9" s="3">
-        <v>216400</v>
       </c>
       <c r="F9" s="3">
         <v>216400</v>
       </c>
       <c r="G9" s="3">
+        <v>216400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>197600</v>
+      </c>
+      <c r="I9" s="3">
         <v>135200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>127100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>127100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>88100</v>
       </c>
       <c r="K9" s="3">
         <v>88100</v>
@@ -817,48 +825,51 @@
         <v>88100</v>
       </c>
       <c r="M9" s="3">
-        <v>91500</v>
+        <v>88100</v>
       </c>
       <c r="N9" s="3">
         <v>91500</v>
       </c>
       <c r="O9" s="3">
-        <v>98000</v>
+        <v>91500</v>
       </c>
       <c r="P9" s="3">
         <v>98000</v>
       </c>
       <c r="Q9" s="3">
-        <v>99800</v>
+        <v>98000</v>
       </c>
       <c r="R9" s="3">
         <v>99800</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3">
+        <v>99800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E10" s="3">
         <v>363300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>220100</v>
       </c>
       <c r="F10" s="3">
         <v>220100</v>
       </c>
       <c r="G10" s="3">
+        <v>220100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>220000</v>
+      </c>
+      <c r="I10" s="3">
         <v>211600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>96000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>96000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>86300</v>
       </c>
       <c r="K10" s="3">
         <v>86300</v>
@@ -867,25 +878,28 @@
         <v>86300</v>
       </c>
       <c r="M10" s="3">
-        <v>83800</v>
+        <v>86300</v>
       </c>
       <c r="N10" s="3">
         <v>83800</v>
       </c>
       <c r="O10" s="3">
-        <v>130000</v>
+        <v>83800</v>
       </c>
       <c r="P10" s="3">
         <v>130000</v>
       </c>
       <c r="Q10" s="3">
-        <v>373100</v>
+        <v>130000</v>
       </c>
       <c r="R10" s="3">
         <v>373100</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3">
+        <v>373100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -904,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -954,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,31 +1022,34 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-98100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-16600</v>
       </c>
       <c r="F14" s="3">
         <v>-16600</v>
       </c>
       <c r="G14" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-62300</v>
+      </c>
+      <c r="I14" s="3">
         <v>25300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-12400</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="J14" s="3">
-        <v>7600</v>
       </c>
       <c r="K14" s="3">
         <v>7600</v>
@@ -1037,48 +1058,51 @@
         <v>7600</v>
       </c>
       <c r="M14" s="3">
-        <v>-6900</v>
+        <v>7600</v>
       </c>
       <c r="N14" s="3">
         <v>-6900</v>
       </c>
       <c r="O14" s="3">
-        <v>600</v>
+        <v>-6900</v>
       </c>
       <c r="P14" s="3">
         <v>600</v>
       </c>
       <c r="Q14" s="3">
-        <v>7300</v>
+        <v>600</v>
       </c>
       <c r="R14" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>103400</v>
+      </c>
+      <c r="E15" s="3">
         <v>108600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>124200</v>
       </c>
       <c r="F15" s="3">
         <v>124200</v>
       </c>
       <c r="G15" s="3">
+        <v>124200</v>
+      </c>
+      <c r="H15" s="3">
+        <v>92700</v>
+      </c>
+      <c r="I15" s="3">
         <v>74600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>86400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>86400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>59600</v>
       </c>
       <c r="K15" s="3">
         <v>59600</v>
@@ -1087,25 +1111,28 @@
         <v>59600</v>
       </c>
       <c r="M15" s="3">
-        <v>75600</v>
+        <v>59600</v>
       </c>
       <c r="N15" s="3">
         <v>75600</v>
       </c>
       <c r="O15" s="3">
-        <v>57500</v>
+        <v>75600</v>
       </c>
       <c r="P15" s="3">
         <v>57500</v>
       </c>
       <c r="Q15" s="3">
-        <v>51900</v>
+        <v>57500</v>
       </c>
       <c r="R15" s="3">
         <v>51900</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>51900</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,31 +1148,32 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E17" s="3">
         <v>924200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>234000</v>
       </c>
       <c r="F17" s="3">
         <v>234000</v>
       </c>
       <c r="G17" s="3">
+        <v>234000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>188500</v>
+      </c>
+      <c r="I17" s="3">
         <v>536600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>280800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>280800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>178300</v>
       </c>
       <c r="K17" s="3">
         <v>178300</v>
@@ -1154,48 +1182,51 @@
         <v>178300</v>
       </c>
       <c r="M17" s="3">
-        <v>64800</v>
+        <v>178300</v>
       </c>
       <c r="N17" s="3">
         <v>64800</v>
       </c>
       <c r="O17" s="3">
-        <v>-223800</v>
+        <v>64800</v>
       </c>
       <c r="P17" s="3">
         <v>-223800</v>
       </c>
       <c r="Q17" s="3">
-        <v>218400</v>
+        <v>-223800</v>
       </c>
       <c r="R17" s="3">
         <v>218400</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3">
+        <v>218400</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>435700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-348700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>202600</v>
       </c>
       <c r="F18" s="3">
         <v>202600</v>
       </c>
       <c r="G18" s="3">
+        <v>202600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>229100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-189800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-57800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-57800</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-3900</v>
       </c>
       <c r="K18" s="3">
         <v>-3900</v>
@@ -1204,25 +1235,28 @@
         <v>-3900</v>
       </c>
       <c r="M18" s="3">
-        <v>110600</v>
+        <v>-3900</v>
       </c>
       <c r="N18" s="3">
         <v>110600</v>
       </c>
       <c r="O18" s="3">
-        <v>451800</v>
+        <v>110600</v>
       </c>
       <c r="P18" s="3">
         <v>451800</v>
       </c>
       <c r="Q18" s="3">
-        <v>254500</v>
+        <v>451800</v>
       </c>
       <c r="R18" s="3">
         <v>254500</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3">
+        <v>254500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,31 +1275,32 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1200</v>
       </c>
       <c r="F20" s="3">
         <v>-1200</v>
       </c>
       <c r="G20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-500</v>
-      </c>
       <c r="J20" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-600</v>
@@ -1274,48 +1309,51 @@
         <v>-600</v>
       </c>
       <c r="M20" s="3">
-        <v>-1700</v>
+        <v>-600</v>
       </c>
       <c r="N20" s="3">
         <v>-1700</v>
       </c>
       <c r="O20" s="3">
-        <v>1800</v>
+        <v>-1700</v>
       </c>
       <c r="P20" s="3">
         <v>1800</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>539800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-239500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>327900</v>
       </c>
       <c r="F21" s="3">
         <v>327900</v>
       </c>
       <c r="G21" s="3">
+        <v>327900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>322600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-114900</v>
       </c>
-      <c r="H21" s="3">
-        <v>29200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>29200</v>
-      </c>
       <c r="J21" s="3">
-        <v>56300</v>
+        <v>28600</v>
       </c>
       <c r="K21" s="3">
         <v>56300</v>
@@ -1324,48 +1362,51 @@
         <v>56300</v>
       </c>
       <c r="M21" s="3">
-        <v>187900</v>
+        <v>56300</v>
       </c>
       <c r="N21" s="3">
         <v>187900</v>
       </c>
       <c r="O21" s="3">
-        <v>507500</v>
+        <v>187900</v>
       </c>
       <c r="P21" s="3">
         <v>507500</v>
       </c>
       <c r="Q21" s="3">
-        <v>306400</v>
+        <v>507500</v>
       </c>
       <c r="R21" s="3">
         <v>306400</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3">
+        <v>306400</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E22" s="3">
         <v>63400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>57700</v>
       </c>
       <c r="F22" s="3">
         <v>57700</v>
       </c>
       <c r="G22" s="3">
+        <v>57700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>56100</v>
+      </c>
+      <c r="I22" s="3">
         <v>42700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>42100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>42100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>26200</v>
       </c>
       <c r="K22" s="3">
         <v>26200</v>
@@ -1374,48 +1415,51 @@
         <v>26200</v>
       </c>
       <c r="M22" s="3">
-        <v>29500</v>
+        <v>26200</v>
       </c>
       <c r="N22" s="3">
         <v>29500</v>
       </c>
       <c r="O22" s="3">
-        <v>30800</v>
+        <v>29500</v>
       </c>
       <c r="P22" s="3">
         <v>30800</v>
       </c>
       <c r="Q22" s="3">
-        <v>27900</v>
+        <v>30800</v>
       </c>
       <c r="R22" s="3">
         <v>27900</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>27900</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>387300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-313400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>164400</v>
       </c>
       <c r="F23" s="3">
         <v>164400</v>
       </c>
       <c r="G23" s="3">
+        <v>164400</v>
+      </c>
+      <c r="H23" s="3">
+        <v>236100</v>
+      </c>
+      <c r="I23" s="3">
         <v>-257500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-82800</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-82800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-41100</v>
       </c>
       <c r="K23" s="3">
         <v>-41100</v>
@@ -1424,48 +1468,51 @@
         <v>-41100</v>
       </c>
       <c r="M23" s="3">
-        <v>86000</v>
+        <v>-41100</v>
       </c>
       <c r="N23" s="3">
         <v>86000</v>
       </c>
       <c r="O23" s="3">
-        <v>414100</v>
+        <v>86000</v>
       </c>
       <c r="P23" s="3">
         <v>414100</v>
       </c>
       <c r="Q23" s="3">
-        <v>215300</v>
+        <v>414100</v>
       </c>
       <c r="R23" s="3">
         <v>215300</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3">
+        <v>215300</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-152800</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-23500</v>
       </c>
       <c r="F24" s="3">
         <v>-23500</v>
       </c>
       <c r="G24" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="I24" s="3">
         <v>65300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-23400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-49000</v>
       </c>
       <c r="K24" s="3">
         <v>-49000</v>
@@ -1474,25 +1521,28 @@
         <v>-49000</v>
       </c>
       <c r="M24" s="3">
-        <v>21700</v>
+        <v>-49000</v>
       </c>
       <c r="N24" s="3">
         <v>21700</v>
       </c>
       <c r="O24" s="3">
-        <v>98700</v>
+        <v>21700</v>
       </c>
       <c r="P24" s="3">
         <v>98700</v>
       </c>
       <c r="Q24" s="3">
-        <v>58000</v>
+        <v>98700</v>
       </c>
       <c r="R24" s="3">
         <v>58000</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,31 +1591,34 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-160700</v>
-      </c>
-      <c r="E26" s="3">
-        <v>187900</v>
       </c>
       <c r="F26" s="3">
         <v>187900</v>
       </c>
       <c r="G26" s="3">
+        <v>187900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>297900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-322800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-59400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-59400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>7900</v>
       </c>
       <c r="K26" s="3">
         <v>7900</v>
@@ -1574,48 +1627,51 @@
         <v>7900</v>
       </c>
       <c r="M26" s="3">
-        <v>64400</v>
+        <v>7900</v>
       </c>
       <c r="N26" s="3">
         <v>64400</v>
       </c>
       <c r="O26" s="3">
-        <v>315500</v>
+        <v>64400</v>
       </c>
       <c r="P26" s="3">
         <v>315500</v>
       </c>
       <c r="Q26" s="3">
-        <v>157300</v>
+        <v>315500</v>
       </c>
       <c r="R26" s="3">
         <v>157300</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3">
+        <v>157300</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-160600</v>
-      </c>
-      <c r="E27" s="3">
-        <v>187800</v>
       </c>
       <c r="F27" s="3">
         <v>187800</v>
       </c>
       <c r="G27" s="3">
+        <v>187800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>297700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-323200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-59700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-59700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>7500</v>
       </c>
       <c r="K27" s="3">
         <v>7500</v>
@@ -1624,25 +1680,28 @@
         <v>7500</v>
       </c>
       <c r="M27" s="3">
-        <v>64000</v>
+        <v>7500</v>
       </c>
       <c r="N27" s="3">
         <v>64000</v>
       </c>
       <c r="O27" s="3">
-        <v>315000</v>
+        <v>64000</v>
       </c>
       <c r="P27" s="3">
         <v>315000</v>
       </c>
       <c r="Q27" s="3">
-        <v>156000</v>
+        <v>315000</v>
       </c>
       <c r="R27" s="3">
         <v>156000</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,31 +1909,34 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1200</v>
       </c>
       <c r="F32" s="3">
         <v>1200</v>
       </c>
       <c r="G32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H32" s="3">
+        <v>800</v>
+      </c>
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
-        <v>500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>500</v>
-      </c>
       <c r="J32" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>600</v>
@@ -1874,48 +1945,51 @@
         <v>600</v>
       </c>
       <c r="M32" s="3">
-        <v>1700</v>
+        <v>600</v>
       </c>
       <c r="N32" s="3">
         <v>1700</v>
       </c>
       <c r="O32" s="3">
-        <v>-1800</v>
+        <v>1700</v>
       </c>
       <c r="P32" s="3">
         <v>-1800</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-160600</v>
-      </c>
-      <c r="E33" s="3">
-        <v>187800</v>
       </c>
       <c r="F33" s="3">
         <v>187800</v>
       </c>
       <c r="G33" s="3">
+        <v>187800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>297700</v>
+      </c>
+      <c r="I33" s="3">
         <v>-323200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-59700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-59700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>7500</v>
       </c>
       <c r="K33" s="3">
         <v>7500</v>
@@ -1924,25 +1998,28 @@
         <v>7500</v>
       </c>
       <c r="M33" s="3">
-        <v>64000</v>
+        <v>7500</v>
       </c>
       <c r="N33" s="3">
         <v>64000</v>
       </c>
       <c r="O33" s="3">
-        <v>315000</v>
+        <v>64000</v>
       </c>
       <c r="P33" s="3">
         <v>315000</v>
       </c>
       <c r="Q33" s="3">
-        <v>156000</v>
+        <v>315000</v>
       </c>
       <c r="R33" s="3">
         <v>156000</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,31 +2068,34 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-160600</v>
-      </c>
-      <c r="E35" s="3">
-        <v>187800</v>
       </c>
       <c r="F35" s="3">
         <v>187800</v>
       </c>
       <c r="G35" s="3">
+        <v>187800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>297700</v>
+      </c>
+      <c r="I35" s="3">
         <v>-323200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-59700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-59700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7500</v>
       </c>
       <c r="K35" s="3">
         <v>7500</v>
@@ -2024,80 +2104,86 @@
         <v>7500</v>
       </c>
       <c r="M35" s="3">
-        <v>64000</v>
+        <v>7500</v>
       </c>
       <c r="N35" s="3">
         <v>64000</v>
       </c>
       <c r="O35" s="3">
-        <v>315000</v>
+        <v>64000</v>
       </c>
       <c r="P35" s="3">
         <v>315000</v>
       </c>
       <c r="Q35" s="3">
-        <v>156000</v>
+        <v>315000</v>
       </c>
       <c r="R35" s="3">
         <v>156000</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45473</v>
       </c>
       <c r="K38" s="2">
         <v>45473</v>
       </c>
       <c r="L38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,31 +2223,32 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>54500</v>
-      </c>
-      <c r="E41" s="3">
-        <v>29700</v>
       </c>
       <c r="F41" s="3">
         <v>29700</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>8</v>
+      <c r="G41" s="3">
+        <v>29700</v>
       </c>
       <c r="H41" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3">
         <v>6000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>3500</v>
       </c>
       <c r="K41" s="3">
         <v>3500</v>
@@ -2169,25 +2257,28 @@
         <v>3500</v>
       </c>
       <c r="M41" s="3">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="N41" s="3">
         <v>3800</v>
       </c>
       <c r="O41" s="3">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="P41" s="3">
         <v>4200</v>
       </c>
       <c r="Q41" s="3">
-        <v>7300</v>
+        <v>4200</v>
       </c>
       <c r="R41" s="3">
         <v>7300</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3">
+        <v>7300</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,31 +2327,34 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>407800</v>
+      </c>
+      <c r="E43" s="3">
         <v>411700</v>
-      </c>
-      <c r="E43" s="3">
-        <v>408400</v>
       </c>
       <c r="F43" s="3">
         <v>408400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
+      <c r="G43" s="3">
+        <v>408400</v>
       </c>
       <c r="H43" s="3">
+        <v>334400</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>234400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>234400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>180000</v>
       </c>
       <c r="K43" s="3">
         <v>180000</v>
@@ -2269,98 +2363,104 @@
         <v>180000</v>
       </c>
       <c r="M43" s="3">
-        <v>190200</v>
+        <v>180000</v>
       </c>
       <c r="N43" s="3">
         <v>190200</v>
       </c>
       <c r="O43" s="3">
-        <v>195000</v>
+        <v>190200</v>
       </c>
       <c r="P43" s="3">
         <v>195000</v>
       </c>
       <c r="Q43" s="3">
-        <v>296800</v>
+        <v>195000</v>
       </c>
       <c r="R43" s="3">
         <v>296800</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>296800</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
-        <v>27800</v>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F44" s="3">
         <v>27800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="G44" s="3">
+        <v>27800</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>9600</v>
       </c>
-      <c r="I44" s="3">
-        <v>9600</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>7800</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>7800</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
+      <c r="O44" s="3">
+        <v>7800</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>9200</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>9200</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E45" s="3">
         <v>76900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>153200</v>
       </c>
       <c r="F45" s="3">
         <v>153200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>153200</v>
       </c>
       <c r="H45" s="3">
+        <v>108600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>33800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>33800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>86900</v>
       </c>
       <c r="K45" s="3">
         <v>86900</v>
@@ -2369,48 +2469,51 @@
         <v>86900</v>
       </c>
       <c r="M45" s="3">
-        <v>87700</v>
+        <v>86900</v>
       </c>
       <c r="N45" s="3">
         <v>87700</v>
       </c>
       <c r="O45" s="3">
-        <v>130700</v>
+        <v>87700</v>
       </c>
       <c r="P45" s="3">
         <v>130700</v>
       </c>
       <c r="Q45" s="3">
-        <v>27700</v>
+        <v>130700</v>
       </c>
       <c r="R45" s="3">
         <v>27700</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>27700</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>551500</v>
+      </c>
+      <c r="E46" s="3">
         <v>627400</v>
-      </c>
-      <c r="E46" s="3">
-        <v>650200</v>
       </c>
       <c r="F46" s="3">
         <v>650200</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>8</v>
+      <c r="G46" s="3">
+        <v>650200</v>
       </c>
       <c r="H46" s="3">
+        <v>487100</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3">
         <v>304300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>304300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>289000</v>
       </c>
       <c r="K46" s="3">
         <v>289000</v>
@@ -2419,63 +2522,66 @@
         <v>289000</v>
       </c>
       <c r="M46" s="3">
-        <v>304600</v>
+        <v>289000</v>
       </c>
       <c r="N46" s="3">
         <v>304600</v>
       </c>
       <c r="O46" s="3">
-        <v>338700</v>
+        <v>304600</v>
       </c>
       <c r="P46" s="3">
         <v>338700</v>
       </c>
       <c r="Q46" s="3">
-        <v>354200</v>
+        <v>338700</v>
       </c>
       <c r="R46" s="3">
         <v>354200</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3">
+        <v>354200</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>10000</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F47" s="3">
         <v>10000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="G47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>6000</v>
       </c>
-      <c r="I47" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>7500</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>7500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
+      <c r="O47" s="3">
+        <v>7500</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -2486,31 +2592,34 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5025200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4918200</v>
-      </c>
-      <c r="E48" s="3">
-        <v>5021600</v>
       </c>
       <c r="F48" s="3">
         <v>5021600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
+      <c r="G48" s="3">
+        <v>5021600</v>
       </c>
       <c r="H48" s="3">
+        <v>4745900</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>3295000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3295000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3173300</v>
       </c>
       <c r="K48" s="3">
         <v>3173300</v>
@@ -2519,25 +2628,28 @@
         <v>3173300</v>
       </c>
       <c r="M48" s="3">
-        <v>2946600</v>
+        <v>3173300</v>
       </c>
       <c r="N48" s="3">
         <v>2946600</v>
       </c>
       <c r="O48" s="3">
-        <v>3155200</v>
+        <v>2946600</v>
       </c>
       <c r="P48" s="3">
         <v>3155200</v>
       </c>
       <c r="Q48" s="3">
-        <v>3018700</v>
+        <v>3155200</v>
       </c>
       <c r="R48" s="3">
         <v>3018700</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>3018700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2545,22 +2657,22 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>3200</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H49" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>2900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J49" s="3">
-        <v>15700</v>
       </c>
       <c r="K49" s="3">
         <v>15700</v>
@@ -2569,25 +2681,28 @@
         <v>15700</v>
       </c>
       <c r="M49" s="3">
-        <v>19400</v>
+        <v>15700</v>
       </c>
       <c r="N49" s="3">
         <v>19400</v>
       </c>
       <c r="O49" s="3">
-        <v>20800</v>
+        <v>19400</v>
       </c>
       <c r="P49" s="3">
         <v>20800</v>
       </c>
       <c r="Q49" s="3">
-        <v>21100</v>
+        <v>20800</v>
       </c>
       <c r="R49" s="3">
         <v>21100</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>21100</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,31 +2804,34 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>220300</v>
+      </c>
+      <c r="E52" s="3">
         <v>254400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>196900</v>
       </c>
       <c r="F52" s="3">
         <v>196900</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
+      <c r="G52" s="3">
+        <v>196900</v>
       </c>
       <c r="H52" s="3">
+        <v>151100</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>77400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>77400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>89600</v>
       </c>
       <c r="K52" s="3">
         <v>89600</v>
@@ -2719,25 +2840,28 @@
         <v>89600</v>
       </c>
       <c r="M52" s="3">
-        <v>51100</v>
+        <v>89600</v>
       </c>
       <c r="N52" s="3">
         <v>51100</v>
       </c>
       <c r="O52" s="3">
-        <v>71600</v>
+        <v>51100</v>
       </c>
       <c r="P52" s="3">
         <v>71600</v>
       </c>
       <c r="Q52" s="3">
-        <v>65800</v>
+        <v>71600</v>
       </c>
       <c r="R52" s="3">
         <v>65800</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>65800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,31 +2910,34 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6109700</v>
+      </c>
+      <c r="E54" s="3">
         <v>6236200</v>
-      </c>
-      <c r="E54" s="3">
-        <v>6169000</v>
       </c>
       <c r="F54" s="3">
         <v>6169000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>8</v>
+      <c r="G54" s="3">
+        <v>6169000</v>
       </c>
       <c r="H54" s="3">
+        <v>5662800</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3">
         <v>3956800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>3956800</v>
-      </c>
-      <c r="J54" s="3">
-        <v>3816500</v>
       </c>
       <c r="K54" s="3">
         <v>3816500</v>
@@ -2819,25 +2946,28 @@
         <v>3816500</v>
       </c>
       <c r="M54" s="3">
-        <v>3474000</v>
+        <v>3816500</v>
       </c>
       <c r="N54" s="3">
         <v>3474000</v>
       </c>
       <c r="O54" s="3">
-        <v>3763000</v>
+        <v>3474000</v>
       </c>
       <c r="P54" s="3">
         <v>3763000</v>
       </c>
       <c r="Q54" s="3">
-        <v>3830900</v>
+        <v>3763000</v>
       </c>
       <c r="R54" s="3">
         <v>3830900</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3">
+        <v>3830900</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,31 +3007,32 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>129500</v>
+      </c>
+      <c r="E57" s="3">
         <v>76400</v>
-      </c>
-      <c r="E57" s="3">
-        <v>81800</v>
       </c>
       <c r="F57" s="3">
         <v>81800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
+      <c r="G57" s="3">
+        <v>81800</v>
       </c>
       <c r="H57" s="3">
+        <v>81300</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>35000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>35000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>60500</v>
       </c>
       <c r="K57" s="3">
         <v>60500</v>
@@ -2909,48 +3041,51 @@
         <v>60500</v>
       </c>
       <c r="M57" s="3">
-        <v>49500</v>
+        <v>60500</v>
       </c>
       <c r="N57" s="3">
         <v>49500</v>
       </c>
       <c r="O57" s="3">
-        <v>69700</v>
+        <v>49500</v>
       </c>
       <c r="P57" s="3">
         <v>69700</v>
       </c>
       <c r="Q57" s="3">
-        <v>90400</v>
+        <v>69700</v>
       </c>
       <c r="R57" s="3">
         <v>90400</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>90400</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E58" s="3">
         <v>235300</v>
-      </c>
-      <c r="E58" s="3">
-        <v>260700</v>
       </c>
       <c r="F58" s="3">
         <v>260700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>260700</v>
       </c>
       <c r="H58" s="3">
+        <v>236100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>223200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>223200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>225300</v>
       </c>
       <c r="K58" s="3">
         <v>225300</v>
@@ -2959,48 +3094,51 @@
         <v>225300</v>
       </c>
       <c r="M58" s="3">
-        <v>211400</v>
+        <v>225300</v>
       </c>
       <c r="N58" s="3">
         <v>211400</v>
       </c>
       <c r="O58" s="3">
-        <v>242500</v>
+        <v>211400</v>
       </c>
       <c r="P58" s="3">
         <v>242500</v>
       </c>
       <c r="Q58" s="3">
-        <v>280400</v>
+        <v>242500</v>
       </c>
       <c r="R58" s="3">
         <v>280400</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>280400</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>555700</v>
+      </c>
+      <c r="E59" s="3">
         <v>865300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>581100</v>
       </c>
       <c r="F59" s="3">
         <v>581100</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
+      <c r="G59" s="3">
+        <v>581100</v>
       </c>
       <c r="H59" s="3">
+        <v>589000</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>435500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>435500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>372200</v>
       </c>
       <c r="K59" s="3">
         <v>372200</v>
@@ -3009,48 +3147,51 @@
         <v>372200</v>
       </c>
       <c r="M59" s="3">
-        <v>277800</v>
+        <v>372200</v>
       </c>
       <c r="N59" s="3">
         <v>277800</v>
       </c>
       <c r="O59" s="3">
-        <v>400900</v>
+        <v>277800</v>
       </c>
       <c r="P59" s="3">
         <v>400900</v>
       </c>
       <c r="Q59" s="3">
-        <v>620700</v>
+        <v>400900</v>
       </c>
       <c r="R59" s="3">
         <v>620700</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3">
+        <v>620700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>969800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1335800</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1075700</v>
       </c>
       <c r="F60" s="3">
         <v>1075700</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>8</v>
+      <c r="G60" s="3">
+        <v>1075700</v>
       </c>
       <c r="H60" s="3">
+        <v>906400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3">
         <v>777100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>777100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>658000</v>
       </c>
       <c r="K60" s="3">
         <v>658000</v>
@@ -3059,48 +3200,51 @@
         <v>658000</v>
       </c>
       <c r="M60" s="3">
-        <v>638400</v>
+        <v>658000</v>
       </c>
       <c r="N60" s="3">
         <v>638400</v>
       </c>
       <c r="O60" s="3">
-        <v>713100</v>
+        <v>638400</v>
       </c>
       <c r="P60" s="3">
         <v>713100</v>
       </c>
       <c r="Q60" s="3">
-        <v>1131600</v>
+        <v>713100</v>
       </c>
       <c r="R60" s="3">
         <v>1131600</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3">
+        <v>1131600</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2844000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2652700</v>
-      </c>
-      <c r="E61" s="3">
-        <v>2767000</v>
       </c>
       <c r="F61" s="3">
         <v>2767000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2767000</v>
       </c>
       <c r="H61" s="3">
+        <v>2524500</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>1526300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1526300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1472300</v>
       </c>
       <c r="K61" s="3">
         <v>1472300</v>
@@ -3109,48 +3253,51 @@
         <v>1472300</v>
       </c>
       <c r="M61" s="3">
-        <v>1096400</v>
+        <v>1472300</v>
       </c>
       <c r="N61" s="3">
         <v>1096400</v>
       </c>
       <c r="O61" s="3">
-        <v>1295500</v>
+        <v>1096400</v>
       </c>
       <c r="P61" s="3">
         <v>1295500</v>
       </c>
       <c r="Q61" s="3">
-        <v>1188800</v>
+        <v>1295500</v>
       </c>
       <c r="R61" s="3">
         <v>1188800</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>1188800</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1334300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1503800</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1319400</v>
       </c>
       <c r="F62" s="3">
         <v>1319400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
+      <c r="G62" s="3">
+        <v>1319400</v>
       </c>
       <c r="H62" s="3">
+        <v>1496500</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
         <v>1233400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1233400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1127000</v>
       </c>
       <c r="K62" s="3">
         <v>1127000</v>
@@ -3159,25 +3306,28 @@
         <v>1127000</v>
       </c>
       <c r="M62" s="3">
-        <v>1127200</v>
+        <v>1127000</v>
       </c>
       <c r="N62" s="3">
         <v>1127200</v>
       </c>
       <c r="O62" s="3">
-        <v>1182200</v>
+        <v>1127200</v>
       </c>
       <c r="P62" s="3">
         <v>1182200</v>
       </c>
       <c r="Q62" s="3">
-        <v>1635700</v>
+        <v>1182200</v>
       </c>
       <c r="R62" s="3">
         <v>1635700</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>1635700</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,31 +3482,34 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5148100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5492300</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5174000</v>
       </c>
       <c r="F66" s="3">
         <v>5174000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>8</v>
+      <c r="G66" s="3">
+        <v>5174000</v>
       </c>
       <c r="H66" s="3">
+        <v>4935100</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3">
         <v>3544900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>3544900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>3268200</v>
       </c>
       <c r="K66" s="3">
         <v>3268200</v>
@@ -3359,25 +3518,28 @@
         <v>3268200</v>
       </c>
       <c r="M66" s="3">
-        <v>2875600</v>
+        <v>3268200</v>
       </c>
       <c r="N66" s="3">
         <v>2875600</v>
       </c>
       <c r="O66" s="3">
-        <v>3202000</v>
+        <v>2875600</v>
       </c>
       <c r="P66" s="3">
         <v>3202000</v>
       </c>
       <c r="Q66" s="3">
-        <v>3968700</v>
+        <v>3202000</v>
       </c>
       <c r="R66" s="3">
         <v>3968700</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3">
+        <v>3968700</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,31 +3768,34 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-468300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-692900</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-507800</v>
       </c>
       <c r="F72" s="3">
         <v>-507800</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
+      <c r="G72" s="3">
+        <v>-507800</v>
       </c>
       <c r="H72" s="3">
+        <v>-802000</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>-759500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-759500</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-591600</v>
       </c>
       <c r="K72" s="3">
         <v>-591600</v>
@@ -3629,25 +3804,28 @@
         <v>-591600</v>
       </c>
       <c r="M72" s="3">
-        <v>-547300</v>
+        <v>-591600</v>
       </c>
       <c r="N72" s="3">
         <v>-547300</v>
       </c>
       <c r="O72" s="3">
-        <v>-590100</v>
+        <v>-547300</v>
       </c>
       <c r="P72" s="3">
         <v>-590100</v>
       </c>
       <c r="Q72" s="3">
-        <v>-1134000</v>
+        <v>-590100</v>
       </c>
       <c r="R72" s="3">
         <v>-1134000</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3">
+        <v>-1134000</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,31 +3980,34 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>950700</v>
+      </c>
+      <c r="E76" s="3">
         <v>733400</v>
-      </c>
-      <c r="E76" s="3">
-        <v>984100</v>
       </c>
       <c r="F76" s="3">
         <v>984100</v>
       </c>
       <c r="G76" s="3">
-        <v>400100</v>
+        <v>984100</v>
       </c>
       <c r="H76" s="3">
-        <v>400100</v>
+        <v>716200</v>
       </c>
       <c r="I76" s="3">
         <v>400100</v>
       </c>
       <c r="J76" s="3">
-        <v>535900</v>
+        <v>400100</v>
       </c>
       <c r="K76" s="3">
         <v>535900</v>
@@ -3829,25 +4016,28 @@
         <v>535900</v>
       </c>
       <c r="M76" s="3">
-        <v>585800</v>
+        <v>535900</v>
       </c>
       <c r="N76" s="3">
         <v>585800</v>
       </c>
       <c r="O76" s="3">
-        <v>547900</v>
+        <v>585800</v>
       </c>
       <c r="P76" s="3">
         <v>547900</v>
       </c>
       <c r="Q76" s="3">
-        <v>-152700</v>
+        <v>547900</v>
       </c>
       <c r="R76" s="3">
         <v>-152700</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3">
+        <v>-152700</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,86 +4086,92 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45565</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45473</v>
       </c>
       <c r="K80" s="2">
         <v>45473</v>
       </c>
       <c r="L80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-160600</v>
-      </c>
-      <c r="E81" s="3">
-        <v>187800</v>
       </c>
       <c r="F81" s="3">
         <v>187800</v>
       </c>
       <c r="G81" s="3">
+        <v>187800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>297700</v>
+      </c>
+      <c r="I81" s="3">
         <v>-323200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-59700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-59700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>7500</v>
       </c>
       <c r="K81" s="3">
         <v>7500</v>
@@ -3984,25 +4180,28 @@
         <v>7500</v>
       </c>
       <c r="M81" s="3">
-        <v>64000</v>
+        <v>7500</v>
       </c>
       <c r="N81" s="3">
         <v>64000</v>
       </c>
       <c r="O81" s="3">
-        <v>315000</v>
+        <v>64000</v>
       </c>
       <c r="P81" s="3">
         <v>315000</v>
       </c>
       <c r="Q81" s="3">
-        <v>156000</v>
+        <v>315000</v>
       </c>
       <c r="R81" s="3">
         <v>156000</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,31 +4220,32 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>74600</v>
+      </c>
+      <c r="F83" s="3">
         <v>86400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>86400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>59600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>59600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>89600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>50900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>57500</v>
       </c>
       <c r="K83" s="3">
         <v>57500</v>
@@ -4054,25 +4254,28 @@
         <v>57500</v>
       </c>
       <c r="M83" s="3">
-        <v>47700</v>
+        <v>57500</v>
       </c>
       <c r="N83" s="3">
         <v>47700</v>
       </c>
       <c r="O83" s="3">
-        <v>59200</v>
+        <v>47700</v>
       </c>
       <c r="P83" s="3">
         <v>59200</v>
       </c>
       <c r="Q83" s="3">
-        <v>43400</v>
+        <v>59200</v>
       </c>
       <c r="R83" s="3">
         <v>43400</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>43400</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,31 +4536,34 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E89" s="3">
         <v>168700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>100200</v>
       </c>
       <c r="F89" s="3">
         <v>100200</v>
       </c>
       <c r="G89" s="3">
+        <v>100200</v>
+      </c>
+      <c r="H89" s="3">
+        <v>80300</v>
+      </c>
+      <c r="I89" s="3">
         <v>84900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>29900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>29900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>80400</v>
       </c>
       <c r="K89" s="3">
         <v>80400</v>
@@ -4354,25 +4572,28 @@
         <v>80400</v>
       </c>
       <c r="M89" s="3">
-        <v>118800</v>
+        <v>80400</v>
       </c>
       <c r="N89" s="3">
         <v>118800</v>
       </c>
       <c r="O89" s="3">
-        <v>86300</v>
+        <v>118800</v>
       </c>
       <c r="P89" s="3">
         <v>86300</v>
       </c>
       <c r="Q89" s="3">
-        <v>91400</v>
+        <v>86300</v>
       </c>
       <c r="R89" s="3">
         <v>91400</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3">
+        <v>91400</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,31 +4612,32 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-259600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-261400</v>
       </c>
       <c r="F91" s="3">
         <v>-261400</v>
       </c>
       <c r="G91" s="3">
+        <v>-261400</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-61200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-78000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-68500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-68500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-98800</v>
       </c>
       <c r="K91" s="3">
         <v>-98800</v>
@@ -4424,25 +4646,28 @@
         <v>-98800</v>
       </c>
       <c r="M91" s="3">
-        <v>-21000</v>
+        <v>-98800</v>
       </c>
       <c r="N91" s="3">
         <v>-21000</v>
       </c>
       <c r="O91" s="3">
-        <v>-147300</v>
+        <v>-21000</v>
       </c>
       <c r="P91" s="3">
         <v>-147300</v>
       </c>
       <c r="Q91" s="3">
-        <v>-127300</v>
+        <v>-147300</v>
       </c>
       <c r="R91" s="3">
         <v>-127300</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>-127300</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,31 +4769,34 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-102800</v>
+      </c>
+      <c r="E94" s="3">
         <v>1300</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-280600</v>
       </c>
       <c r="F94" s="3">
         <v>-280600</v>
       </c>
       <c r="G94" s="3">
+        <v>-280600</v>
+      </c>
+      <c r="H94" s="3">
+        <v>9100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-405000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-41600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-41600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-91800</v>
       </c>
       <c r="K94" s="3">
         <v>-91800</v>
@@ -4574,25 +4805,28 @@
         <v>-91800</v>
       </c>
       <c r="M94" s="3">
-        <v>5300</v>
+        <v>-91800</v>
       </c>
       <c r="N94" s="3">
         <v>5300</v>
       </c>
       <c r="O94" s="3">
-        <v>-125000</v>
+        <v>5300</v>
       </c>
       <c r="P94" s="3">
         <v>-125000</v>
       </c>
       <c r="Q94" s="3">
-        <v>-132200</v>
+        <v>-125000</v>
       </c>
       <c r="R94" s="3">
         <v>-132200</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>-132200</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,31 +4845,32 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E96" s="3">
         <v>22100</v>
-      </c>
-      <c r="E96" s="3">
-        <v>22600</v>
       </c>
       <c r="F96" s="3">
         <v>22600</v>
       </c>
       <c r="G96" s="3">
+        <v>22600</v>
+      </c>
+      <c r="H96" s="3">
+        <v>22700</v>
+      </c>
+      <c r="I96" s="3">
         <v>17200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>14400</v>
-      </c>
-      <c r="I96" s="3">
-        <v>14400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>27500</v>
       </c>
       <c r="K96" s="3">
         <v>27500</v>
@@ -4644,7 +4879,7 @@
         <v>27500</v>
       </c>
       <c r="M96" s="3">
-        <v>42000</v>
+        <v>27500</v>
       </c>
       <c r="N96" s="3">
         <v>42000</v>
@@ -4656,13 +4891,16 @@
         <v>42000</v>
       </c>
       <c r="Q96" s="3">
-        <v>35600</v>
+        <v>42000</v>
       </c>
       <c r="R96" s="3">
         <v>35600</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>35600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,31 +5055,34 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-159700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>217900</v>
       </c>
       <c r="F100" s="3">
         <v>217900</v>
       </c>
       <c r="G100" s="3">
+        <v>217900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-101200</v>
+      </c>
+      <c r="I100" s="3">
         <v>406600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>17900</v>
-      </c>
-      <c r="I100" s="3">
-        <v>17900</v>
-      </c>
-      <c r="J100" s="3">
-        <v>11300</v>
       </c>
       <c r="K100" s="3">
         <v>11300</v>
@@ -4844,25 +5091,28 @@
         <v>11300</v>
       </c>
       <c r="M100" s="3">
-        <v>-124300</v>
+        <v>11300</v>
       </c>
       <c r="N100" s="3">
         <v>-124300</v>
       </c>
       <c r="O100" s="3">
-        <v>37200</v>
+        <v>-124300</v>
       </c>
       <c r="P100" s="3">
         <v>37200</v>
       </c>
       <c r="Q100" s="3">
-        <v>-49200</v>
+        <v>37200</v>
       </c>
       <c r="R100" s="3">
         <v>-49200</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>-49200</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4911,31 +5161,34 @@
       <c r="R101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52100</v>
+      </c>
+      <c r="E102" s="3">
         <v>10400</v>
-      </c>
-      <c r="E102" s="3">
-        <v>37500</v>
       </c>
       <c r="F102" s="3">
         <v>37500</v>
       </c>
       <c r="G102" s="3">
+        <v>37500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="I102" s="3">
         <v>86400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-100</v>
       </c>
       <c r="K102" s="3">
         <v>-100</v>
@@ -4944,21 +5197,24 @@
         <v>-100</v>
       </c>
       <c r="M102" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="N102" s="3">
         <v>-200</v>
       </c>
       <c r="O102" s="3">
-        <v>-1600</v>
+        <v>-200</v>
       </c>
       <c r="P102" s="3">
         <v>-1600</v>
       </c>
       <c r="Q102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="R102" s="3">
         <v>-90000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-90000</v>
       </c>
     </row>
